--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2603,62 +2603,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154348</v>
+        <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>99377</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strandåker, Strandåker, Jmt</t>
+          <t>Z716 Hällesjö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555070</v>
+        <v>554907</v>
       </c>
       <c r="R19" t="n">
-        <v>6961372</v>
+        <v>6961502</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,12 +2668,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,74 +2688,69 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128154348</t>
+          <t>https://artportalen.se/Sighting/136547033</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96790354</v>
+        <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>91402</v>
+        <v>108105</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>256703</v>
+        <v>219933</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dragsjömon, Jmt</t>
+          <t>Z716 Hällesjö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555101</v>
+        <v>555125</v>
       </c>
       <c r="R20" t="n">
-        <v>6961358</v>
+        <v>6961294</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2793,12 +2774,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,90 +2788,75 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>äldre sandtallskog, i stig</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96790354</t>
+          <t>https://artportalen.se/Sighting/136540093</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96790371</v>
+        <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>91402</v>
+        <v>108105</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>256703</v>
+        <v>219933</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dragsjömon, Jmt</t>
+          <t>Z716 Hällesjö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555037</v>
+        <v>555079</v>
       </c>
       <c r="R21" t="n">
-        <v>6961430</v>
+        <v>6961320</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2914,12 +2880,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,90 +2894,75 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>yngre sandtallskog med tunt förnatäcke intill äldre tallskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96790371</t>
+          <t>https://artportalen.se/Sighting/136540890</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96790381</v>
+        <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>91402</v>
+        <v>108105</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>256703</v>
+        <v>219933</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dragsjömon, Jmt</t>
+          <t>Z716 Hällesjö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>554931</v>
+        <v>554987</v>
       </c>
       <c r="R22" t="n">
-        <v>6961560</v>
+        <v>6961424</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3035,12 +2986,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3049,84 +3000,75 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog med fina lavpartier</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96790381</t>
+          <t>https://artportalen.se/Sighting/136541348</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121310741</v>
+        <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>91402</v>
+        <v>108105</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256703</v>
+        <v>219933</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dragsjömoarna, Jmt</t>
+          <t>Z716 Hällesjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555134</v>
+        <v>554989</v>
       </c>
       <c r="R23" t="n">
-        <v>6961338</v>
+        <v>6961406</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3150,12 +3092,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,23 +3106,1353 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136546743</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136547162</v>
+      </c>
+      <c r="B24" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Z716 Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>555106</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6961295</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136547162</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136547347</v>
+      </c>
+      <c r="B25" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Z716 Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>555075</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6961312</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136547347</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136547731</v>
+      </c>
+      <c r="B26" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Z716 Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>555084</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6961305</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136547731</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136549841</v>
+      </c>
+      <c r="B27" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Z716 Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>554933</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6961472</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136549841</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136550335</v>
+      </c>
+      <c r="B28" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Z716 Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>554976</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6961435</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136550335</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128154348</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Strandåker, Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>555070</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6961372</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154348</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136540285</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99619</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Z716 Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>554941</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6961463</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136540285</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136542340</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99619</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Z716 Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>554942</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6961476</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136542340</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>96790354</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dragsjömon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>555101</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6961358</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog, i stig</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790354</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>96790371</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dragsjömon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>555037</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6961430</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>yngre sandtallskog med tunt förnatäcke intill äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790371</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>96790381</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dragsjömon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>554931</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6961560</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med fina lavpartier</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790381</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121310741</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dragsjömoarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>555134</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6961338</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Anton Björk</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Anton Björk</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121310741</t>
         </is>
@@ -3210,6 +4482,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99628</v>
+        <v>99630</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99628</v>
+        <v>99630</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99639</v>
+        <v>99645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99639</v>
+        <v>99645</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99645</v>
+        <v>99649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99645</v>
+        <v>99649</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99649</v>
+        <v>99651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99649</v>
+        <v>99651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99651</v>
+        <v>99653</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99651</v>
+        <v>99653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99653</v>
+        <v>99666</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99653</v>
+        <v>99666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -2606,7 +2606,7 @@
         <v>136547033</v>
       </c>
       <c r="B19" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136540093</v>
       </c>
       <c r="B20" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136540890</v>
       </c>
       <c r="B21" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136541348</v>
       </c>
       <c r="B22" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>136546743</v>
       </c>
       <c r="B23" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136547162</v>
       </c>
       <c r="B24" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136547347</v>
       </c>
       <c r="B25" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136547731</v>
       </c>
       <c r="B26" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136549841</v>
       </c>
       <c r="B27" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136550335</v>
       </c>
       <c r="B28" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136540285</v>
       </c>
       <c r="B30" t="n">
-        <v>99666</v>
+        <v>99668</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136542340</v>
       </c>
       <c r="B31" t="n">
-        <v>99666</v>
+        <v>99668</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
